--- a/Assets/Game/luban/config/general/avatar.xlsx
+++ b/Assets/Game/luban/config/general/avatar.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -129,6 +129,39 @@
   </si>
   <si>
     <t>默认头像</t>
+  </si>
+  <si>
+    <t>头像-1</t>
+  </si>
+  <si>
+    <t>头像-2</t>
+  </si>
+  <si>
+    <t>头像-3</t>
+  </si>
+  <si>
+    <t>头像-4</t>
+  </si>
+  <si>
+    <t>头像-5</t>
+  </si>
+  <si>
+    <t>头像-6</t>
+  </si>
+  <si>
+    <t>头像-7</t>
+  </si>
+  <si>
+    <t>头像-8</t>
+  </si>
+  <si>
+    <t>头像-9</t>
+  </si>
+  <si>
+    <t>头像-10</t>
+  </si>
+  <si>
+    <t>头像-11</t>
   </si>
 </sst>
 </file>
@@ -1316,15 +1349,15 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="3"/>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
     <col min="2" max="2" width="18.125" style="2" customWidth="1"/>
     <col min="3" max="3" width="29.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="12.75" style="2" customWidth="1"/>
     <col min="5" max="5" width="12.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.125" style="2" customWidth="1"/>
     <col min="8" max="8" width="16.625" style="2" customWidth="1"/>
     <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
@@ -1458,6 +1491,10 @@
       <c r="E4" s="2">
         <v>1</v>
       </c>
+      <c r="F4" s="2" t="str">
+        <f>"Assets/Game/Textures/Avatar/"&amp;B4&amp;".png"</f>
+        <v>Assets/Game/Textures/Avatar/400001.png</v>
+      </c>
       <c r="H4" s="2">
         <v>0</v>
       </c>
@@ -1465,11 +1502,308 @@
         <v>0</v>
       </c>
       <c r="J4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="B5" s="2">
+        <v>400002</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f t="shared" ref="F5:F15" si="0">"Assets/Game/Textures/Avatar/"&amp;B5&amp;".png"</f>
+        <v>Assets/Game/Textures/Avatar/400002.png</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" s="2">
+        <v>400003</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400003.png</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="B7" s="2">
+        <v>400004</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400004.png</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" s="2">
+        <v>400005</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400005.png</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="B9" s="2">
+        <v>400006</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400006.png</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="B10" s="2">
+        <v>400007</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400007.png</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="B11" s="2">
+        <v>400008</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400008.png</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="B12" s="2">
+        <v>400009</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400009.png</v>
+      </c>
+      <c r="H12" s="2">
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="B13" s="2">
+        <v>400010</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400010.png</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" s="2">
+        <v>400011</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400011.png</v>
+      </c>
+      <c r="H14" s="2">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" s="2">
+        <v>400012</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Assets/Game/Textures/Avatar/400012.png</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C5" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C15" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">

--- a/Assets/Game/luban/config/general/avatar.xlsx
+++ b/Assets/Game/luban/config/general/avatar.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -53,12 +53,6 @@
     <t>full_res</t>
   </si>
   <si>
-    <t>unlock_type</t>
-  </si>
-  <si>
-    <t>unlock_param</t>
-  </si>
-  <si>
     <t>hidden</t>
   </si>
   <si>
@@ -83,9 +77,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>task_event_type</t>
-  </si>
-  <si>
     <t>bool</t>
   </si>
   <si>
@@ -111,12 +102,6 @@
   </si>
   <si>
     <t>详情时的资源路径</t>
-  </si>
-  <si>
-    <t>解锁条件类型</t>
-  </si>
-  <si>
-    <t>解锁条件参数</t>
   </si>
   <si>
     <t>未解锁时是否在列表中可见</t>
@@ -1349,7 +1334,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -1359,15 +1344,13 @@
     <col min="5" max="5" width="12.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="37.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="16.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="25.375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="27.125" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="25.375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="27.125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1398,92 +1381,74 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:10">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1" t="s">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:10">
       <c r="B4" s="2">
         <v>400001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -1495,22 +1460,16 @@
         <f>"Assets/Game/Textures/Avatar/"&amp;B4&amp;".png"</f>
         <v>Assets/Game/Textures/Avatar/400001.png</v>
       </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="b">
+      <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:10">
       <c r="B5" s="2">
         <v>400002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
@@ -1522,22 +1481,16 @@
         <f t="shared" ref="F5:F15" si="0">"Assets/Game/Textures/Avatar/"&amp;B5&amp;".png"</f>
         <v>Assets/Game/Textures/Avatar/400002.png</v>
       </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2" t="b">
+      <c r="H5" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:10">
       <c r="B6" s="2">
         <v>400003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
@@ -1549,22 +1502,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400003.png</v>
       </c>
-      <c r="H6" s="2">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2">
-        <v>0</v>
-      </c>
-      <c r="J6" s="2" t="b">
+      <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:10">
       <c r="B7" s="2">
         <v>400004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -1576,22 +1523,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400004.png</v>
       </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2" t="b">
+      <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:10">
       <c r="B8" s="2">
         <v>400005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
@@ -1603,22 +1544,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400005.png</v>
       </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
-      <c r="J8" s="2" t="b">
+      <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:10">
       <c r="B9" s="2">
         <v>400006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
@@ -1630,22 +1565,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400006.png</v>
       </c>
-      <c r="H9" s="2">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="b">
+      <c r="H9" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:10">
       <c r="B10" s="2">
         <v>400007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
@@ -1657,22 +1586,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400007.png</v>
       </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
-      <c r="J10" s="2" t="b">
+      <c r="H10" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:10">
       <c r="B11" s="2">
         <v>400008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -1684,22 +1607,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400008.png</v>
       </c>
-      <c r="H11" s="2">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
-      <c r="J11" s="2" t="b">
+      <c r="H11" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:10">
       <c r="B12" s="2">
         <v>400009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -1711,22 +1628,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400009.png</v>
       </c>
-      <c r="H12" s="2">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="b">
+      <c r="H12" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:10">
       <c r="B13" s="2">
         <v>400010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -1738,22 +1649,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400010.png</v>
       </c>
-      <c r="H13" s="2">
-        <v>0</v>
-      </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
-      <c r="J13" s="2" t="b">
+      <c r="H13" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:10">
       <c r="B14" s="2">
         <v>400011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
@@ -1765,22 +1670,16 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400011.png</v>
       </c>
-      <c r="H14" s="2">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
-      <c r="J14" s="2" t="b">
+      <c r="H14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:10">
       <c r="B15" s="2">
         <v>400012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
@@ -1792,13 +1691,7 @@
         <f t="shared" si="0"/>
         <v>Assets/Game/Textures/Avatar/400012.png</v>
       </c>
-      <c r="H15" s="2">
-        <v>0</v>
-      </c>
-      <c r="I15" s="2">
-        <v>0</v>
-      </c>
-      <c r="J15" s="2" t="b">
+      <c r="H15" s="2" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Game/luban/config/general/avatar.xlsx
+++ b/Assets/Game/luban/config/general/avatar.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -56,6 +56,9 @@
     <t>hidden</t>
   </si>
   <si>
+    <t>is_open</t>
+  </si>
+  <si>
     <t>desc</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
     <t>未解锁时是否在列表中可见</t>
   </si>
   <si>
+    <t>英雄是否开放</t>
+  </si>
+  <si>
     <t>获取途径描述文案</t>
   </si>
   <si>
@@ -116,37 +122,28 @@
     <t>默认头像</t>
   </si>
   <si>
-    <t>头像-1</t>
-  </si>
-  <si>
-    <t>头像-2</t>
-  </si>
-  <si>
-    <t>头像-3</t>
-  </si>
-  <si>
-    <t>头像-4</t>
-  </si>
-  <si>
-    <t>头像-5</t>
-  </si>
-  <si>
-    <t>头像-6</t>
-  </si>
-  <si>
-    <t>头像-7</t>
-  </si>
-  <si>
-    <t>头像-8</t>
-  </si>
-  <si>
-    <t>头像-9</t>
-  </si>
-  <si>
-    <t>头像-10</t>
-  </si>
-  <si>
-    <t>头像-11</t>
+    <t>头像-嬴政</t>
+  </si>
+  <si>
+    <t>头像-刘彻</t>
+  </si>
+  <si>
+    <t>头像-李世民</t>
+  </si>
+  <si>
+    <t>头像-赵飞燕</t>
+  </si>
+  <si>
+    <t>头像-蔡文姬</t>
+  </si>
+  <si>
+    <t>头像-杨玉环</t>
+  </si>
+  <si>
+    <t>头像-白起</t>
+  </si>
+  <si>
+    <t>头像-张骞</t>
   </si>
 </sst>
 </file>
@@ -1334,7 +1331,7 @@
   <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="32.8833333333333" style="2" customWidth="1"/>
@@ -1344,13 +1341,13 @@
     <col min="5" max="5" width="12.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="37.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="17.125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="27.125" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="8" max="9" width="25.375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="27.125" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1381,329 +1378,379 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>16</v>
+      <c r="K2" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="203.1" customHeight="1" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:11">
       <c r="B4" s="2">
-        <v>400001</v>
+        <v>4011001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2">
+        <f>IF(B4="","",MOD(INT(B4/1000),10))</f>
         <v>1</v>
       </c>
       <c r="E4" s="2">
+        <f>IF(B4="","",MOD(INT(B4/10000),10))</f>
         <v>1</v>
       </c>
       <c r="F4" s="2" t="str">
         <f>"Assets/Game/Textures/Avatar/"&amp;B4&amp;".png"</f>
-        <v>Assets/Game/Textures/Avatar/400001.png</v>
+        <v>Assets/Game/Textures/Avatar/4011001.png</v>
       </c>
       <c r="H4" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="I4" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="B5" s="2">
-        <v>400002</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="str">
-        <f t="shared" ref="F5:F15" si="0">"Assets/Game/Textures/Avatar/"&amp;B5&amp;".png"</f>
-        <v>Assets/Game/Textures/Avatar/400002.png</v>
-      </c>
-      <c r="H5" s="2" t="b">
-        <v>1</v>
+    <row r="5" spans="1:11">
+      <c r="D5" s="2" t="str">
+        <f>IF(B5="","",MOD(INT(B5/1000),10))</f>
+        <v/>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f>IF(B5="","",MOD(INT(B5/10000),10))</f>
+        <v/>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="B6" s="2">
-        <v>400003</v>
+        <v>4024001</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <f>IF(B6="","",MOD(INT(B6/1000),10))</f>
+        <v>4</v>
       </c>
       <c r="E6" s="2">
-        <v>1</v>
+        <f>IF(B6="","",MOD(INT(B6/10000),10))</f>
+        <v>2</v>
       </c>
       <c r="F6" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400003.png</v>
+        <f>"Assets/Game/Textures/Avatar/"&amp;B6&amp;".png"</f>
+        <v>Assets/Game/Textures/Avatar/4024001.png</v>
       </c>
       <c r="H6" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="I6" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="B7" s="2">
-        <v>400004</v>
+        <v>4024002</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <f>IF(B7="","",MOD(INT(B7/1000),10))</f>
+        <v>4</v>
       </c>
       <c r="E7" s="2">
-        <v>1</v>
+        <f>IF(B7="","",MOD(INT(B7/10000),10))</f>
+        <v>2</v>
       </c>
       <c r="F7" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400004.png</v>
+        <f>"Assets/Game/Textures/Avatar/"&amp;B7&amp;".png"</f>
+        <v>Assets/Game/Textures/Avatar/4024002.png</v>
       </c>
       <c r="H7" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="I7" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="B8" s="2">
-        <v>400005</v>
+        <v>4024003</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="2">
-        <v>1</v>
+        <f>IF(B8="","",MOD(INT(B8/1000),10))</f>
+        <v>4</v>
       </c>
       <c r="E8" s="2">
-        <v>1</v>
+        <f>IF(B8="","",MOD(INT(B8/10000),10))</f>
+        <v>2</v>
       </c>
       <c r="F8" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400005.png</v>
+        <f>"Assets/Game/Textures/Avatar/"&amp;B8&amp;".png"</f>
+        <v>Assets/Game/Textures/Avatar/4024003.png</v>
       </c>
       <c r="H8" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="I8" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="2">
-        <v>400006</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400006.png</v>
-      </c>
-      <c r="H9" s="2" t="b">
-        <v>1</v>
+    <row r="9" spans="1:11">
+      <c r="D9" s="2" t="str">
+        <f t="shared" ref="D9:D16" si="0">IF(B9="","",MOD(INT(B9/1000),10))</f>
+        <v/>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f t="shared" ref="E9:E16" si="1">IF(B9="","",MOD(INT(B9/10000),10))</f>
+        <v/>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="B10" s="2">
-        <v>400007</v>
+        <v>4034001</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="E10" s="2">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400007.png</v>
+        <f t="shared" ref="F9:F16" si="2">"Assets/Game/Textures/Avatar/"&amp;B10&amp;".png"</f>
+        <v>Assets/Game/Textures/Avatar/4034001.png</v>
       </c>
       <c r="H10" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="I10" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="B11" s="2">
-        <v>400008</v>
+        <v>4034002</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="2">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="E11" s="2">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="str">
-        <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400008.png</v>
+        <f t="shared" si="2"/>
+        <v>Assets/Game/Textures/Avatar/4034002.png</v>
       </c>
       <c r="H11" s="2" t="b">
         <v>1</v>
       </c>
+      <c r="I11" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="B12" s="2">
-        <v>400009</v>
+        <v>4034003</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D12" s="2">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3</v>
       </c>
       <c r="F12" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Assets/Game/Textures/Avatar/4034003.png</v>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="D13" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400009.png</v>
-      </c>
-      <c r="H12" s="2" t="b">
-        <v>1</v>
+        <v/>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v/>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="2">
-        <v>400010</v>
-      </c>
-      <c r="C13" s="2" t="s">
+    <row r="14" spans="1:11">
+      <c r="B14" s="2">
+        <v>4044001</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1</v>
-      </c>
-      <c r="F13" s="2" t="str">
+      <c r="D14" s="2">
         <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400010.png</v>
-      </c>
-      <c r="H13" s="2" t="b">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Assets/Game/Textures/Avatar/4044001.png</v>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="2">
-        <v>400011</v>
-      </c>
-      <c r="C14" s="2" t="s">
+    <row r="15" spans="1:11">
+      <c r="B15" s="2">
+        <v>4044002</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="2">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1</v>
-      </c>
-      <c r="F14" s="2" t="str">
+      <c r="D15" s="2">
         <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400011.png</v>
-      </c>
-      <c r="H14" s="2" t="b">
+        <v>4</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Assets/Game/Textures/Avatar/4044002.png</v>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2">
-        <v>400012</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1</v>
-      </c>
-      <c r="F15" s="2" t="str">
+    <row r="16" spans="1:11">
+      <c r="B16" s="2">
+        <v>4044003</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2">
         <f t="shared" si="0"/>
-        <v>Assets/Game/Textures/Avatar/400012.png</v>
-      </c>
-      <c r="H15" s="2" t="b">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Assets/Game/Textures/Avatar/4044003.png</v>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C15" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C9" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:B16">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B$1:B$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+  <conditionalFormatting sqref="B1:B9 B17:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Game/luban/config/general/avatar.xlsx
+++ b/Assets/Game/luban/config/general/avatar.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Item!$A$3:$C$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -110,7 +110,7 @@
     <t>未解锁时是否在列表中可见</t>
   </si>
   <si>
-    <t>英雄是否开放</t>
+    <t>头像是否开放</t>
   </si>
   <si>
     <t>获取途径描述文案</t>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>头像-张骞</t>
+  </si>
+  <si>
+    <t>头像-房玄龄</t>
   </si>
 </sst>
 </file>
@@ -1718,7 +1721,7 @@
         <v>4044003</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="2">
         <f t="shared" si="0"/>
@@ -1740,7 +1743,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C9" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A3:C12" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="D3">
